--- a/docs/반응형외피_경제성자료.xlsx
+++ b/docs/반응형외피_경제성자료.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="4" name="3_차폐·냉방환산" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="4_결정회의안건" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="5_1784운영규칙" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="6_태양궤적(분석)" state="visible" r:id="rId10"/>
+    <sheet sheetId="7" name="6_태양궤적(혜연)" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="7_공사비" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="8_시공전후" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="9_발주처이익" state="visible" r:id="rId13"/>
@@ -37,13 +37,13 @@
     <t>작성</t>
   </si>
   <si>
-    <t>총괄 (보고서·경제성·PM)</t>
+    <t>은미 (보고서·경제성·PM)</t>
   </si>
   <si>
     <t>시트 구성</t>
   </si>
   <si>
-    <t>1_입력값 / 2_단가조사 / 3_차폐·냉방환산 / 4_결정회의안건 / 5_1784운영규칙 / 6_태양궤적(분석) / 7_공사비 / 8_시공전후 / 9_발주처이익 / 10_누적·민감도 / 11_인센티브 / 12_일정표 / 13_탄소·계절효과 / 14_Radiance(팀) / 15_웹도구</t>
+    <t>1_입력값 / 2_단가조사 / 3_차폐·냉방환산 / 4_결정회의안건 / 5_1784운영규칙 / 6_태양궤적(혜연) / 7_공사비 / 8_시공전후 / 9_발주처이익 / 10_누적·민감도 / 11_인센티브 / 12_일정표 / 13_탄소·계절효과 / 14_Radiance(팀) / 15_웹도구</t>
   </si>
   <si>
     <t>색 규칙</t>
@@ -55,7 +55,7 @@
     <t>중요</t>
   </si>
   <si>
-    <t>임시값과 빈칸은 실제 조사 결과가 아닙니다. 출처를 확인하고 상태를 바꾼 뒤에만 보고서에 쓰세요. 2_단가조사의 숫자는 공개 자료로 확인되지 않아 제가 넣은 추정치입니다. 5_1784운영규칙과 6_태양궤적은 분석의 자료입니다.</t>
+    <t>임시값과 빈칸은 실제 조사 결과가 아닙니다. 출처를 확인하고 상태를 바꾼 뒤에만 보고서에 쓰세요. 2_단가조사의 숫자는 공개 자료로 확인되지 않아 제가 넣은 추정치입니다. 5_1784운영규칙과 6_태양궤적은 혜연의 자료입니다.</t>
   </si>
   <si>
     <t>2일차 연결</t>
@@ -91,7 +91,7 @@
     <t>임시 테스트값</t>
   </si>
   <si>
-    <t>주황색 칸(창 면적, 루버 면적, 일사량, 조명 사용량 등)은 계산이 되는지 보려고 제가 넣은 임시값입니다. 모델링·분석·실내의 실제 값으로 교체하기 전의 결과는 보고서에 쓰지 마세요.</t>
+    <t>주황색 칸(창 면적, 루버 면적, 일사량, 조명 사용량 등)은 계산이 되는지 보려고 제가 넣은 임시값입니다. 우정·혜연·서우의 실제 값으로 교체하기 전의 결과는 보고서에 쓰지 마세요.</t>
   </si>
   <si>
     <t>넘겨받는 분께</t>
@@ -154,10 +154,10 @@
     <t>네이버 1784 (OSM). 웹 · Radiance 와 같은 좌표 (예전 값 37.35936 은 그린팩토리)</t>
   </si>
   <si>
-    <t>분석</t>
-  </si>
-  <si>
-    <t>입력 (분석 자료)</t>
+    <t>혜연</t>
+  </si>
+  <si>
+    <t>입력 (혜연 자료)</t>
   </si>
   <si>
     <t>경도</t>
@@ -175,13 +175,13 @@
     <t>춘분 3/21 · 하지 6/21 · 추분 9/23 · 동지 12/21</t>
   </si>
   <si>
-    <t>분석은 4일을 제시. 계획서는 3일(하지·춘추분·동지) → 회의에서 확정</t>
+    <t>혜연은 4일을 제시. 계획서는 3일(하지·춘추분·동지) → 회의에서 확정</t>
   </si>
   <si>
     <t>전원</t>
   </si>
   <si>
-    <t>분석 제안, 확정 필요</t>
+    <t>혜연 제안, 확정 필요</t>
   </si>
   <si>
     <t>입면</t>
@@ -208,7 +208,7 @@
     <t>분석 입면 기준, Revit</t>
   </si>
   <si>
-    <t>모델링</t>
+    <t>우정</t>
   </si>
   <si>
     <t>루버 설치면 합계 (아래 53~60행)</t>
@@ -220,7 +220,7 @@
     <t>대표 실 조건표</t>
   </si>
   <si>
-    <t>실내</t>
+    <t>서우</t>
   </si>
   <si>
     <t>미입력</t>
@@ -271,7 +271,7 @@
     <t>외부 설치 가설 일수 (곤돌라·고소작업)</t>
   </si>
   <si>
-    <t>총괄</t>
+    <t>은미</t>
   </si>
   <si>
     <t>임시 테스트값 (실제값으로 교체)</t>
@@ -379,7 +379,7 @@
     <t>kWh/㎡·년</t>
   </si>
   <si>
-    <t>분석 GH 결과(대표일→연간)</t>
+    <t>혜연 GH 결과(대표일→연간)</t>
   </si>
   <si>
     <t>4일차 수령</t>
@@ -397,7 +397,7 @@
     <t>kWh/년</t>
   </si>
   <si>
-    <t>실내 Honeybee 결과</t>
+    <t>서우 Honeybee 결과</t>
   </si>
   <si>
     <t>확장</t>
@@ -427,7 +427,7 @@
     <t>°</t>
   </si>
   <si>
-    <t>분석 팀 가정값. 5_1784운영규칙 시트 참조</t>
+    <t>혜연 팀 가정값. 5_1784운영규칙 시트 참조</t>
   </si>
   <si>
     <t>가정 (±15° 민감도 예정)</t>
@@ -514,7 +514,7 @@
     <t>kWh/㎡ (냉방기 6~9월, 1784 1~28층 평균, 창 면적 가중)</t>
   </si>
   <si>
-    <t>분석 GH 결과(연 환산) · 동·남·서면 창 면적 가중 평균, 북면 제외</t>
+    <t>혜연 GH 결과(연 환산) · 동·남·서면 창 면적 가중 평균, 북면 제외</t>
   </si>
   <si>
     <t>일사량 - 내부 반응형</t>
@@ -523,7 +523,7 @@
     <t>kWh/㎡ (냉방기, 1~28층 평균) = 통유리 − 0.45 × (통유리 − 외부 반응형)</t>
   </si>
   <si>
-    <t>분석 GH 결과</t>
+    <t>혜연 GH 결과</t>
   </si>
   <si>
     <t>일사량 - 외부 고정</t>
@@ -550,7 +550,7 @@
     <t>스위치 (0: 일사량이 이미 루버를 반영한 Radiance 값이라 끔)</t>
   </si>
   <si>
-    <t>분석 일사량이 루버 차폐를 이미 반영했다면 0 (이중계산 방지, 안건 6번)</t>
+    <t>혜연 일사량이 루버 차폐를 이미 반영했다면 0 (이중계산 방지, 안건 6번)</t>
   </si>
   <si>
     <t>구동 유닛 수 (내부 반응형)</t>
@@ -586,7 +586,7 @@
     <t>창 면적 - 동면</t>
   </si>
   <si>
-    <t>Revit (모델링)</t>
+    <t>Revit (우정)</t>
   </si>
   <si>
     <t>창 면적 - 남면</t>
@@ -598,7 +598,7 @@
     <t>창 면적 - 북면</t>
   </si>
   <si>
-    <t>Revit (모델링) · 루버 없음</t>
+    <t>Revit (우정) · 루버 없음</t>
   </si>
   <si>
     <t>루버 설치 - 동면 (1/0)</t>
@@ -895,7 +895,7 @@
     <t>이중계산 주의</t>
   </si>
   <si>
-    <t>분석의 일사량이 루버 기하까지 반영한 값이면 차양계수를 또 곱하면 이중계산입니다. 결정회의 안건 6번에서 정의하세요.</t>
+    <t>혜연의 일사량이 루버 기하까지 반영한 값이면 차양계수를 또 곱하면 이중계산입니다. 결정회의 안건 6번에서 정의하세요.</t>
   </si>
   <si>
     <t>※ 실제 계산은 8_시공전후 시트에서 이 차양계수 표(기준 열)를 가져다 씁니다.</t>
@@ -925,7 +925,7 @@
     <t>1_입력값 시트</t>
   </si>
   <si>
-    <t>총괄 진행</t>
+    <t>은미 진행</t>
   </si>
   <si>
     <t>분석 입면</t>
@@ -937,7 +937,7 @@
     <t>입면 사진, 배치도</t>
   </si>
   <si>
-    <t>모델링·분석</t>
+    <t>우정·혜연</t>
   </si>
   <si>
     <t>대표 실</t>
@@ -952,13 +952,13 @@
     <t>대표일 3개 vs 4개</t>
   </si>
   <si>
-    <t>계획서는 3일(하지·춘추분·동지)인데 분석은 춘분 3/21·하지 6/21·추분 9/23·동지 12/21 4일로 계산함 → 4일로 갈지 확정, 연간 환산 가중치(각 대표일이 약 3개월 대표) 정의</t>
+    <t>계획서는 3일(하지·춘추분·동지)인데 혜연은 춘분 3/21·하지 6/21·추분 9/23·동지 12/21 4일로 계산함 → 4일로 갈지 확정, 연간 환산 가중치(각 대표일이 약 3개월 대표) 정의</t>
   </si>
   <si>
     <t>가중치 합의</t>
   </si>
   <si>
-    <t>분석·실내</t>
+    <t>혜연·서우</t>
   </si>
   <si>
     <t>대안 4개 정의</t>
@@ -973,13 +973,13 @@
     <t>차양계수 이중계산 방지</t>
   </si>
   <si>
-    <t>분석의 일사량이 루버 차폐를 이미 반영하는지, 차양계수는 무엇에만 적용할지</t>
+    <t>혜연의 일사량이 루버 차폐를 이미 반영하는지, 차양계수는 무엇에만 적용할지</t>
   </si>
   <si>
     <t>3_차폐·냉방환산 시트</t>
   </si>
   <si>
-    <t>분석·총괄</t>
+    <t>혜연·은미</t>
   </si>
   <si>
     <t>데이터 전달 형식</t>
@@ -1012,7 +1012,7 @@
     <t>스탠드업 시간·장소. 3일 저녁 Unity 기준(모델이 열리고 태양을 날짜·시각으로 움직일 수 있나), 5일 아침 반사광 기준(4일차까지 세 대안 경제성 표가 나왔나)</t>
   </si>
   <si>
-    <t>1784 개폐 시각 (분석 · 검증용 가정 시나리오 v1, 2026.10.06)</t>
+    <t>1784 개폐 시각 (혜연 · 검증용 가정 시나리오 v1, 2026.10.06)</t>
   </si>
   <si>
     <t>규칙: 태양 방위와 입면 정면의 방위차가 컷오프 이하이고 태양 고도 5° 이상이면 닫고, 아니면 연다. 공개 자료에 방위별 개폐 시각이 없어 태양 위치로 계산한 가정이다.</t>
@@ -1180,13 +1180,13 @@
     <t>삼우TV 영상 11:19 - 동서남북 4방향별 수직 루버 타공률이 다름</t>
   </si>
   <si>
-    <t>건축사신문, heyPOP 등 기사 - 방위별 개폐 수치 없음(분석 확인)</t>
+    <t>건축사신문, heyPOP 등 기사 - 방위별 개폐 수치 없음(혜연 확인)</t>
   </si>
   <si>
     <t>컷오프·최소 고도는 팀 가정값. 흐린 날, 주변 건물 그림자, 조도는 반영하지 않음</t>
   </si>
   <si>
-    <t>입면 방위는 지도 기준이라 모델링 모델과 대조 필요</t>
+    <t>입면 방위는 지도 기준이라 우정 모델과 대조 필요</t>
   </si>
   <si>
     <t>hoy</t>
@@ -1480,7 +1480,7 @@
     <t>① 공사비 산출 — 얼마 드나</t>
   </si>
   <si>
-    <t>모든 단가는 2_단가조사 기준값 × 단가 배율. 물량은 1_입력값(모델링 Revit 일람표). 루버는 동·남·서면에만 설치(북면 제외). 시공 전(일반 통유리)은 공사비 0.</t>
+    <t>모든 단가는 2_단가조사 기준값 × 단가 배율. 물량은 1_입력값(우정 Revit 일람표). 루버는 동·남·서면에만 설치(북면 제외). 시공 전(일반 통유리)은 공사비 0.</t>
   </si>
   <si>
     <t>산출 근거</t>
@@ -1693,7 +1693,7 @@
     <t>구동장치 교체비 반영: 보호 유리 안 · 실내 10년, 바깥 노출 5년마다 구동 유닛 전체 교체 (8_시공전후 13행). 에너지 절감에 난방 증가분 포함.</t>
   </si>
   <si>
-    <t>누적 비용 (공사비 + 운영비 누적) — 시각화에게 그래프 디자인용 데이터</t>
+    <t>누적 비용 (공사비 + 운영비 누적) — 건우에게 그래프 디자인용 데이터</t>
   </si>
   <si>
     <t>전기요금 연 인상률 반영. 엑셀에서 A~E열을 선택 → 삽입 → 꺾은선 차트로 바로 그릴 수 있습니다. 선이 교차하는 연도가 회수 연도입니다.</t>
@@ -1786,7 +1786,7 @@
     <t>유리한 조합 (단가-30%, 전기+30%)</t>
   </si>
   <si>
-    <t>방위별 회수 기간(동·남·서향)은 5일차에 분석의 방위별 일사량이 오면 1_입력값 36~39행을 방위별로 바꿔 돌린 값을 기록할 표를 추가합니다.</t>
+    <t>방위별 회수 기간(동·남·서향)은 5일차에 혜연의 방위별 일사량이 오면 1_입력값 36~39행을 방위별로 바꿔 돌린 값을 기록할 표를 추가합니다.</t>
   </si>
   <si>
     <t>인증 인센티브 (신축 / 리모델링) — 가정값, 기본은 꺼짐</t>
@@ -1966,13 +1966,13 @@
     <t>루버 패밀리 파라미터 이름 합의</t>
   </si>
   <si>
-    <t>파라미터 이름표 → 총괄 참조</t>
+    <t>파라미터 이름표 → 은미 참조</t>
   </si>
   <si>
     <t>분석·보고서 조</t>
   </si>
   <si>
-    <t>단가 확정, 모델링 물량으로 공사비 1차</t>
+    <t>단가 확정, 우정 물량으로 공사비 1차</t>
   </si>
   <si>
     <t>작동하는 시트 → 전원</t>
@@ -1981,13 +1981,13 @@
     <t>저녁 관통에 시트 연결</t>
   </si>
   <si>
-    <t>총괄·분석</t>
+    <t>은미·혜연</t>
   </si>
   <si>
     <t>Unity 판단 회의 (모델이 열리고 태양을 날짜·시각으로 움직이나)</t>
   </si>
   <si>
-    <t>총괄 진행(시각화·분석)</t>
+    <t>은미 진행(건우·혜연)</t>
   </si>
   <si>
     <t>Unity 결정 → 전원</t>
@@ -1999,7 +1999,7 @@
     <t>③ 적용</t>
   </si>
   <si>
-    <t>분석 일사량 → 냉방 전력 환산, 실내 조명 값 반영</t>
+    <t>혜연 일사량 → 냉방 전력 환산, 서우 조명 값 반영</t>
   </si>
   <si>
     <t>시공 전후 비교·발주처 이익 1차</t>
@@ -2017,7 +2017,7 @@
     <t>반사광 판단 회의 (4일차까지 세 대안 경제성 표가 나왔나)</t>
   </si>
   <si>
-    <t>총괄 진행(분석)</t>
+    <t>은미 진행(혜연)</t>
   </si>
   <si>
     <t>5일차 아침</t>
@@ -2026,7 +2026,7 @@
     <t>민감도, 누적 비용 그래프, 방위별 회수 기간</t>
   </si>
   <si>
-    <t>그래프 → 시각화(디자인)</t>
+    <t>그래프 → 건우(디자인)</t>
   </si>
   <si>
     <t>보고서 5장 초안</t>
@@ -2047,10 +2047,10 @@
     <t>결론과 권고, 부록(가정값·출처·적용 범위)</t>
   </si>
   <si>
-    <t>모델링 최종 물량과 보고서 공사비 대조</t>
-  </si>
-  <si>
-    <t>총괄·모델링</t>
+    <t>우정 최종 물량과 보고서 공사비 대조</t>
+  </si>
+  <si>
+    <t>은미·우정</t>
   </si>
   <si>
     <t>함께·발표 준비</t>
@@ -2062,13 +2062,13 @@
     <t>팀원 예상 질문 취합, 리허설 시간 재기</t>
   </si>
   <si>
-    <t>예상 질문 묶음 → 분석</t>
+    <t>예상 질문 묶음 → 혜연</t>
   </si>
   <si>
     <t>매일 저녁 스탠드업</t>
   </si>
   <si>
-    <t>10분: 오늘 한 것 · 막힌 것 · 내일 할 것 · 판단 지점. 파일 하나에 주인 한 명, 파일 사이는 CSV, 공유 Revit 모델 수정은 모델링만.</t>
+    <t>10분: 오늘 한 것 · 막힌 것 · 내일 할 것 · 판단 지점. 파일 하나에 주인 한 명, 파일 사이는 CSV, 공유 Revit 모델 수정은 우정만.</t>
   </si>
   <si>
     <t>④ 탄소 · 계절 효과 — 친환경 관점 (통유리 대비)</t>
@@ -2362,7 +2362,7 @@
     <t>⑦ 층별 solar_result — 1784 1~28층 평균 (지금 엑셀 계산에 쓰는 값)</t>
   </si>
   <si>
-    <t>출처: Floor_Solar_Result.json (분석, 팀 v9). Radiance, 서울(성남) TMY 월평균, 주변 건물 325개 그림자를 층 높이마다 적용 (해가 반 이상 막히면 날 열림), 면 중앙 1㎡, 날 폭 300 / 간격 350 / 반사율 0.5. 냉방기 6~9월 · 난방기 11~3월. 단위 kWh/㎡ (계절 합계). 1~28층 평균 = 사이 층은 직선 보간, 1~2층은 3층 값, 26~28층은 25층 값 (오른쪽 층 가중치 ÷ 28).</t>
+    <t>출처: Floor_Solar_Result.json (혜연, 팀 v9). Radiance, 서울(성남) TMY 월평균, 주변 건물 325개 그림자를 층 높이마다 적용 (해가 반 이상 막히면 날 열림), 면 중앙 1㎡, 날 폭 300 / 간격 350 / 반사율 0.5. 냉방기 6~9월 · 난방기 11~3월. 단위 kWh/㎡ (계절 합계). 1~28층 평균 = 사이 층은 직선 보간, 1~2층은 3층 값, 26~28층은 25층 값 (오른쪽 층 가중치 ÷ 28).</t>
   </si>
   <si>
     <t>층</t>

--- a/docs/반응형외피_경제성자료.xlsx
+++ b/docs/반응형외피_경제성자료.xlsx
@@ -2578,10 +2578,10 @@
     <t>화면 비율</t>
   </si>
   <si>
-    <t>지도 · Unity · 웹 3D 3:1</t>
-  </si>
-  <si>
-    <t>보고서 캡처 · 인쇄 화면은 가운데 2:1</t>
+    <t>지도 · Unity · 웹 3D 2:1</t>
+  </si>
+  <si>
+    <t>보고서 캡처 · 인쇄 화면도 2:1</t>
   </si>
   <si>
     <t>브이월드 인증키</t>
@@ -9355,7 +9355,7 @@
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>792</v>
       </c>
@@ -9917,7 +9917,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
